--- a/docs/poc_2026-05-06.xlsx
+++ b/docs/poc_2026-05-06.xlsx
@@ -495,14 +495,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -540,11 +539,6 @@
           <t>产品能力</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>交付时间</t>
-        </is>
-      </c>
     </row>
     <row r="5" ht="75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -567,11 +561,6 @@
           <t>AI 自动整合客户提交材料 + 内部知识库 + CRM 主键数据 · 字段一致性比对率 ≥ 95% · 自动识别财报与工商登记的矛盾(如注册资本与实缴差异 · 法人变更)·所有判断可追溯到原文出处。</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="6" ht="75" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -594,11 +583,6 @@
           <t>基于客户经营材料自动抽取风险点 / 担保类型 / 行业标签 · 每条标签必带原文出处与判断依据 · 证据可追溯率 100% · 标签准确率 ≥ 80%。</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -621,11 +605,6 @@
           <t>基于已成交客户画像 + 公开信号(招投标/工商/纳税/招聘) · 推荐 Top 10 相似企业 · 每条推荐附 4 维度匹配证据(行业/规模/区域/经营信号)·客户经理可一键查看证据链。</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="75" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -648,11 +627,6 @@
           <t>细分 8 类客群(行业龙头 / 成长期 / 科创 / 小微 / 产业链上下游 / 高风险待观察 / 出口型 / 数字化转型) · 4 层产品金字塔(战略 / 核心 / 创新 / 普惠) · 自动给出适配产品 + 不适配原因 + 风险等级。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="75" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -675,11 +649,6 @@
           <t>三重合规防线:授信决策红线规则 + 合规政策实时矩阵对比 + 决策上链审计 · 红线触发即阻断 · 监管检查可全链路追溯。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="75" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -702,11 +671,6 @@
           <t>针对每位客户生成定制化沟通话术(开场 / 关键卖点 / 异议处理 / 结束语 4 段)·按 8 类客群分发不同模板 · 与传统规则模板对照测试中 LLM 路径胜率显著领先。</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="75" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -729,11 +693,6 @@
           <t>审贷决策建议(通过 / 拒绝 / 补件)+ 额度 / 期限 / 利率 + 红线提示 + 一键回写报告闭环 · 每条决策上链审计 · 监管可独立查证。</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="12" ht="75" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -756,11 +715,6 @@
           <t>端到端响应延迟监测 · 单点查询 P50 ≤ 5 秒 · 复杂多 Agent 链路 P95 ≤ 12 秒 · 上线前完成压力测试并向客户公布真实 SLA。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="13" ht="75" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -783,11 +737,6 @@
           <t>三重防幻觉机制:证据优先生成(每条结论必引证)+ 确定性计算优先(财务比率走 Python · LLM 不算确定性)+ 输出终审(占位符未填即标记 '未能自动填写' · 不编)。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
     <row r="14" ht="75" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -810,16 +759,11 @@
           <t>敏感字段(统社 / 身份证 / 法人电话)自动哈希 · 决策上链含脱敏审计 + 客户数据物理隔离(永不多租户)+ ECS 私有化部署 + 大模型全境内调用(符合 PIPL 跨境数据合规)。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>已上线</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/poc_2026-05-06.xlsx
+++ b/docs/poc_2026-05-06.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>基于客户经营材料自动抽取风险点 / 担保类型 / 行业标签 · 每条标签必带原文出处与判断依据 · 证据可追溯率 100% · 标签准确率 ≥ 80%。</t>
+          <t>基于客户经营材料自动抽取风险点 / 担保类型 / 行业标签 · 每条标签必带原文出处与判断依据 · 证据可追溯率 100% · 标签准确率经行业 baseline 验证后公布(目标 ≥ 80%)。</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>针对每位客户生成定制化沟通话术(开场 / 关键卖点 / 异议处理 / 结束语 4 段)·按 8 类客群分发不同模板 · 与传统规则模板对照测试中 LLM 路径胜率显著领先。</t>
+          <t>针对每位客户生成定制化沟通话术(开场 / 关键卖点 / 异议处理 / 结束语 4 段)·按 8 类客群分发不同模板 · 内置基于客户名称 / 行业 / 经营特征的证据引用 · 相比传统规则模板更贴合客户实际场景(具体效果数据 A/B 测试后公布)。</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>端到端响应延迟监测 · 单点查询 P50 ≤ 5 秒 · 复杂多 Agent 链路 P95 ≤ 12 秒 · 上线前完成压力测试并向客户公布真实 SLA。</t>
+          <t>端到端响应延迟全量监测 · 单点查询(候选推荐 / 风险扫描)目标 P50 ≤ 5 秒 · 多 Agent 业务流程(报告生成 / 审贷决策链路)目标视场景而定 · 上线前完成压力测试并向客户公布真实 SLA。</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Q4 · 商业化闭环</t>
+          <t>Q4 起 · 商业化扩展</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>营销活动闭环(决策 → CRM 回写 → 营销活动 → ROI 跟踪)· 接入更多业务线(零售 / 普惠 / 公司业务三口一体)</t>
+          <t>决策 → CRM 回写 → 营销活动 → ROI 跟踪 闭环 · 按银行实际节奏分阶段推进 · 接入更多业务线(零售 / 普惠 / 公司业务)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">

--- a/docs/poc_2026-05-06.xlsx
+++ b/docs/poc_2026-05-06.xlsx
@@ -507,14 +507,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>授信 AI 助手 · POC 评估表</t>
+          <t>个人金融 AI 助手 · POC 评估表</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>面向银行客户经理 / 审贷员 / 合规官 / 风险经理 · 私有化部署 · 永不 multi-tenant</t>
+          <t>面向个金客户经理 / 理财顾问 / 风险经理 / 合规官 · 私有化部署 · 永不 multi-tenant</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="80" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>一、客户画像</t>
@@ -558,11 +558,11 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>AI 自动整合客户提交材料 + 内部知识库 + CRM 主键数据 · 字段一致性比对率 ≥ 95% · 自动识别财报与工商登记的矛盾(如注册资本与实缴差异 · 法人变更)·所有判断可追溯到原文出处。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
+          <t>AI 自动整合个人客户提交资料(身份证 / 工作证明 / 收入流水 / 征信报告 / 资产证明) + 内部知识库 + CRM 主键(身份证号)· 字段一致性比对率 ≥ 95% · 自动识别矛盾(如收入流水与工作证明 / 资产证明与负债的差异)·所有判断可追溯到原始材料出处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>一、客户画像</t>
@@ -575,16 +575,16 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>1.2 标签提取深度</t>
+          <t>1.2 隐性标签提取</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>基于客户经营材料自动抽取风险点 / 担保类型 / 行业标签 · 每条标签必带原文出处与判断依据 · 证据可追溯率 100% · 标签准确率经行业 baseline 验证后公布(目标 ≥ 80%)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>基于客户基础资料 + 历史交易行为 + 公开信号(社保 / 公积金 / 不动产)自动抽取隐性标签:风险偏好(保守 / 稳健 / 平衡 / 进取)/ 投资风格 / 消费习惯 / 生命周期阶段(新参 / 成长 / 成熟 / 退休)/ 家庭责任 · 每条标签必带原始数据出处与判断依据 · 证据可追溯率 100% · 标签准确率经业务 baseline 验证后公布(目标 ≥ 80%)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>一、客户画像</t>
@@ -602,11 +602,11 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>基于已成交客户画像 + 公开信号(招投标/工商/纳税/招聘) · 推荐 Top 10 相似企业 · 每条推荐附 4 维度匹配证据(行业/规模/区域/经营信号)·客户经理可一键查看证据链。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+          <t>基于个人画像 + 历史持仓 + 行为信号(账户活跃度 / 资金流入流出 / 季节性周期)· 预测下一步金融需求(理财升级 / 子女教育金 / 房贷申请 / 退休规划 / 保险续保 / 跨境配置)· 推荐 Top 10 适配产品 · 每条推荐附 4 维度匹配证据(生命周期 / 风险偏好 / 资产水平 / 家庭责任)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="80" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>二、产品适配</t>
@@ -624,11 +624,11 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>细分 8 类客群(行业龙头 / 成长期 / 科创 / 小微 / 产业链上下游 / 高风险待观察 / 出口型 / 数字化转型) · 4 层产品金字塔(战略 / 核心 / 创新 / 普惠) · 自动给出适配产品 + 不适配原因 + 风险等级。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
+          <t>财富分层(大众 / 富裕 / 高净值 / 私人银行) × 全产品矩阵(储蓄 / 现金管理 / 理财 / 公募基金 / 私募基金 / 保险 / 信托 / 消费贷 / 信用卡 / 房贷 / 车贷)· 自动给出适配产品 + 不适配原因 + 风险等级 + 投资期限匹配建议。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="80" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>二、产品适配</t>
@@ -646,11 +646,11 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>三重合规防线:授信决策红线规则 + 合规政策实时矩阵对比 + 决策上链审计 · 红线触发即阻断 · 监管检查可全链路追溯。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
+          <t>三重合规防线:适当性销售合规(KYC + 风险偏好评估 + 双录)+ 反洗钱筛查 + 个人征信合规规则 + 决策上链审计 · 不匹配风险偏好的产品自动阻断 · 监管检查全链路追溯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="80" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>三、经营策略</t>
@@ -663,16 +663,16 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>3.1 策略方案可执行性</t>
+          <t>3.1 客户运营话术</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>针对每位客户生成定制化沟通话术(开场 / 关键卖点 / 异议处理 / 结束语 4 段)·按 8 类客群分发不同模板 · 内置基于客户名称 / 行业 / 经营特征的证据引用 · 相比传统规则模板更贴合客户实际场景(具体效果数据 A/B 测试后公布)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
+          <t>针对每位客户生成定制化运营话术 · 覆盖完整生命周期场景:首次邀约 / 激活转化 / 持有复购 / 防流失挽留 · 每段话术含开场切入 / 价值卖点 / 异议处理 / 促成动作 4 段 · 按客户分层与生命周期分发不同模板 · 内置基于客户姓名 / 资产 / 家庭情况的证据引用 · 相比传统规则模板更贴合实际场景(具体效果 A/B 测试后公布)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="80" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>三、经营策略</t>
@@ -685,16 +685,16 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>3.2 决策建议可执行</t>
+          <t>3.2 任务拆解与 KPI 追踪</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>审贷决策建议(通过 / 拒绝 / 补件)+ 额度 / 期限 / 利率 + 红线提示 + 一键回写报告闭环 · 每条决策上链审计 · 监管可独立查证。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="75" customHeight="1">
+          <t>客户运营建议(推荐产品 / 推荐时机 / 推荐渠道 / 触达频次) + KPI 自动跟踪(AUM 增长 / 产品持有数 / 复购率 / 流失率) + 任务自动拆解(电话 / 短信 / 面谈 / 线上推送) + 一键回写客户档案 · 每条决策上链审计 · 营销动作可独立查证。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="80" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>四、技术性能</t>
@@ -712,11 +712,11 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>端到端响应延迟全量监测 · 单点查询(候选推荐 / 风险扫描)目标 P50 ≤ 5 秒 · 多 Agent 业务流程(报告生成 / 审贷决策链路)目标视场景而定 · 上线前完成压力测试并向客户公布真实 SLA。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>端到端响应延迟全量监测 · 单点查询(画像查询 / 产品推荐)目标 P50 ≤ 5 秒 · 多 Agent 业务流程(完整客户洞察 + 合规校验 + 营销建议)目标视场景而定 · 上线前完成压力测试并向客户公布真实 SLA。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="80" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>四、技术性能</t>
@@ -734,11 +734,11 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>三重防幻觉机制:证据优先生成(每条结论必引证)+ 确定性计算优先(财务比率走 Python · LLM 不算确定性)+ 输出终审(占位符未填即标记 '未能自动填写' · 不编)。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="75" customHeight="1">
+          <t>三重防幻觉机制:证据优先生成(每条客户标签 / 产品推荐必引证)+ 确定性计算优先(资产配置比 / 投资期限 / 利率走 Python 规则)+ 输出终审(数据缺失即标记 '未能自动填写' · 绝不编造)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>四、技术性能</t>
@@ -756,7 +756,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>敏感字段(统社 / 身份证 / 法人电话)自动哈希 · 决策上链含脱敏审计 + 客户数据物理隔离(永不多租户)+ ECS 私有化部署 + 大模型全境内调用(符合 PIPL 跨境数据合规)。</t>
+          <t>敏感字段(身份证号 / 手机号 / 银行卡号 / 资产明细)自动哈希 · 决策上链含脱敏审计 + 客户数据物理隔离(永不多租户)+ ECS 私有化部署 + 大模型全境内调用(符合 PIPL 跨境数据合规)+ 个人金融监管底线全覆盖。</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>1</t>
@@ -826,7 +826,7 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>授信报告 → 决策评分 → 合规对比 → 贷后预警 全链路联动 · 客户经理 / 审贷员 / 合规官 / 风险经理 在同一平台协同 · 一笔授信从材料到放款全流程可追溯。</t>
+          <t>个人金融场景全链路联动:客户洞察 → 适当性销售校验 → 风险偏好评估 → 营销策略生成 → 客户行为预警 · 个金客户经理 / 理财顾问 / 风险经理 / 合规官在同一平台协同 · 一笔营销动作从客户画像到最终触达全流程可追溯。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -835,7 +835,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -848,7 +848,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>5 类用户角色(客户经理 / 审贷员 / 合规官 / 风险经理 / 管理员) × 6 个 Agent 真权限隔离 · 客户经理不可调风控参数 · 合规官不可改授信结论 · 严格行级隔离。</t>
+          <t>5 类用户角色(个金客户经理 / 理财顾问 / 风险经理 / 合规官 / 管理员) × 6 个 Agent 真权限隔离 · 客户经理不可调风险参数 · 合规官不可改营销话术 · 严格行级隔离。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>3</t>
@@ -870,7 +870,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>确定性计算优先(财务指标走 Python 规则)+ 证据优先生成(每条结论必引证)+ 输出终审(占位符未填即标记 '未能自动填写' · 绝不编造)。</t>
+          <t>确定性计算优先(资产配置比 / 投资期限 / 利率公式走 Python 规则)+ 证据优先生成(每条客户标签 / 产品推荐 / 话术内容必引证)+ 输出终审(数据缺失即标记 '未能自动填写' · 绝不编造)。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -879,7 +879,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7" ht="85" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -892,7 +892,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>每一笔授信决策 / 报告生成 / 合规判定都上链(本地 SQLite)· 含敏感数据哈希 + 跨地区分级保留(总行 5 年 / 分行 90 天)· 监管检查可独立查证。</t>
+          <t>每一笔产品推荐 / 适当性判定 / 营销决策都上链(本地 SQLite)· 含敏感数据哈希 + 跨地区分级保留(总行 5 年 / 分行 90 天)· 监管检查可独立查证 · 满足个人金融监管要求。</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -901,7 +901,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8" ht="85" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>5</t>
@@ -914,12 +914,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>全境内大模型调用(符合 PIPL)· 客户数据物理隔离(永不多租户)· ECS 私有化部署 · 审计日志含数据出境标识 · 满足银保监 / 央行最严要求。</t>
+          <t>全境内大模型调用(符合 PIPL · 个人金融数据合规底线)· 客户数据物理隔离(永不多租户)· ECS 私有化部署 · 审计日志含数据出境标识 · 满足银保监 / 央行 / 个人信息保护法最严要求。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>海外 SaaS 产品(Moody's / FICO)无 PIPL 合规支撑</t>
+          <t>海外 SaaS 产品(Moody's / FICO 等)无 PIPL 合规支撑</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -969,7 +969,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>当前已上线</t>
@@ -977,16 +977,16 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>6 Agent 全栈(获客 / 报告 / 授信 / 风控 / 合规 / 预警)· 客户角色权限管控 · 决策上链审计 · 私有化部署</t>
+          <t>6 Agent 全栈服务个人金融业务(客户洞察 / 客户档案 / 个人授信 / 风险预警 / 适当性合规 / 零售策略)· 5 类用户角色权限管控 · 决策上链审计 · 私有化部署</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>客户经理可立即接入 · 走 Demo 全流程 · 客户走访验收</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
+          <t>个金客户经理可立即接入 · 走个人客户全流程 Demo · 客户走访验收</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="85" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Q2 · 客户运行验证</t>
@@ -994,33 +994,33 @@
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>客户实际业务跑通 · 端到端 SLA 真值采集(P50 / P95 实际响应延迟)· 标签准确率 baseline 公布 · 业务数据闭环</t>
+          <t>客户实际个人金融业务跑通 · 端到端 SLA 真值采集(P50 / P95 实际响应延迟)· 客户标签准确率 baseline 公布 · 客户 AUM 增长数据闭环</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>向银行管理层提交季度运行报告 · 用真实数据替代演示数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
+          <t>向银行管理层提交季度运行报告 · 用真实业务数据替代演示数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Q3 · 行业深化</t>
+          <t>Q3 · 业务深化</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>对接客户银行 CRM 实际数据 · 8 类客群细分模型上线 + 4 层产品金字塔正式启用 · 千人千面话术库扩展至 30+ 行业模板</t>
+          <t>对接客户银行 CRM 实际数据 · 财富分层模型(大众 / 富裕 / 高净值 / 私行)上线 + 全产品矩阵(储蓄 / 理财 / 基金 / 保险 / 信贷)正式启用 · 千人千面话术库覆盖主要客户分层与生命周期场景</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>客户经理工作效率提升 30%+ · 拓客转化率提升 · 适配方案命中率 ≥ 95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
+          <t>客户经理工作效率显著提升 · 邀约 / 激活 / 复购转化率提升 · 适配方案命中率持续优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="85" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Q4 起 · 商业化扩展</t>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>决策 → CRM 回写 → 营销活动 → ROI 跟踪 闭环 · 按银行实际节奏分阶段推进 · 接入更多业务线(零售 / 普惠 / 公司业务)</t>
+          <t>营销活动闭环(决策 → CRM 回写 → 营销活动 → ROI 跟踪)· 按银行实际节奏分阶段推进 · 接入更多业务场景(私人银行 / 普惠零售 / 线上银行多触点)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>AI 助手成为客户经理日常工作平台 · 直接驱动业务量与收入</t>
+          <t>AI 助手成为客户经理日常工作平台 · 直接驱动 AUM 与客户活跃度增长</t>
         </is>
       </c>
     </row>
